--- a/panchang-data/London2026.xlsx
+++ b/panchang-data/London2026.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9518" uniqueCount="5418">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9518" uniqueCount="5419">
   <si>
     <t>दिनाङ्क</t>
   </si>
@@ -16282,6 +16282,9 @@
   </si>
   <si>
     <t>121°04'11.12</t>
+  </si>
+  <si>
+    <t>ज्येष्ठ अधिक</t>
   </si>
 </sst>
 </file>
@@ -16771,7 +16774,7 @@
         <v>46023</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>29</v>
@@ -16857,7 +16860,7 @@
         <v>46024</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>51</v>
@@ -16943,7 +16946,7 @@
         <v>46025</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>70</v>
@@ -17029,7 +17032,7 @@
         <v>46026</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>89</v>
+        <v>573</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>90</v>
@@ -17115,7 +17118,7 @@
         <v>46027</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>89</v>
+        <v>573</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>110</v>
@@ -17201,7 +17204,7 @@
         <v>46028</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>89</v>
+        <v>573</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>127</v>
@@ -17287,7 +17290,7 @@
         <v>46029</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>89</v>
+        <v>573</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>144</v>
@@ -17373,7 +17376,7 @@
         <v>46030</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>89</v>
+        <v>573</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>29</v>
@@ -17459,7 +17462,7 @@
         <v>46031</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>89</v>
+        <v>573</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>51</v>
@@ -17545,7 +17548,7 @@
         <v>46032</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>89</v>
+        <v>573</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>70</v>
@@ -17631,7 +17634,7 @@
         <v>46033</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>89</v>
+        <v>573</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>90</v>
@@ -17717,7 +17720,7 @@
         <v>46034</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>89</v>
+        <v>573</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>110</v>
@@ -17803,7 +17806,7 @@
         <v>46035</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>89</v>
+        <v>573</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>127</v>
@@ -17889,7 +17892,7 @@
         <v>46036</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>89</v>
+        <v>573</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>144</v>
@@ -17975,7 +17978,7 @@
         <v>46037</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>89</v>
+        <v>573</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>29</v>
@@ -18061,7 +18064,7 @@
         <v>46038</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>89</v>
+        <v>573</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>51</v>
@@ -18147,7 +18150,7 @@
         <v>46039</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>89</v>
+        <v>573</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>70</v>
@@ -18233,7 +18236,7 @@
         <v>46040</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>89</v>
+        <v>573</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>90</v>
@@ -18319,7 +18322,7 @@
         <v>46041</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>89</v>
+        <v>573</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>110</v>
@@ -18405,7 +18408,7 @@
         <v>46042</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>89</v>
+        <v>573</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>127</v>
@@ -18491,7 +18494,7 @@
         <v>46043</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>89</v>
+        <v>573</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>144</v>
@@ -18577,7 +18580,7 @@
         <v>46044</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>89</v>
+        <v>573</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>29</v>
@@ -18663,7 +18666,7 @@
         <v>46045</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>89</v>
+        <v>573</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>51</v>
@@ -18749,7 +18752,7 @@
         <v>46046</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>89</v>
+        <v>573</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>70</v>
@@ -18835,7 +18838,7 @@
         <v>46047</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>89</v>
+        <v>573</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>90</v>
@@ -18921,7 +18924,7 @@
         <v>46048</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>89</v>
+        <v>573</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>110</v>
@@ -19007,7 +19010,7 @@
         <v>46049</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>89</v>
+        <v>573</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>127</v>
@@ -19093,7 +19096,7 @@
         <v>46050</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>89</v>
+        <v>573</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>144</v>
@@ -19179,7 +19182,7 @@
         <v>46051</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>89</v>
+        <v>573</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>29</v>
@@ -19265,7 +19268,7 @@
         <v>46052</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>89</v>
+        <v>573</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>51</v>
@@ -19351,7 +19354,7 @@
         <v>46053</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>89</v>
+        <v>573</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>70</v>
@@ -19437,7 +19440,7 @@
         <v>46054</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>89</v>
+        <v>573</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>90</v>
@@ -19523,7 +19526,7 @@
         <v>46055</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>573</v>
+        <v>1012</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>110</v>
@@ -19609,7 +19612,7 @@
         <v>46056</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>573</v>
+        <v>1012</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>127</v>
@@ -19695,7 +19698,7 @@
         <v>46057</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>573</v>
+        <v>1012</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>144</v>
@@ -19781,7 +19784,7 @@
         <v>46058</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>573</v>
+        <v>1012</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>29</v>
@@ -19867,7 +19870,7 @@
         <v>46059</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>573</v>
+        <v>1012</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>51</v>
@@ -19953,7 +19956,7 @@
         <v>46060</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>573</v>
+        <v>1012</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>70</v>
@@ -20039,7 +20042,7 @@
         <v>46061</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>573</v>
+        <v>1012</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>90</v>
@@ -20125,7 +20128,7 @@
         <v>46062</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>573</v>
+        <v>1012</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>110</v>
@@ -20211,7 +20214,7 @@
         <v>46063</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>573</v>
+        <v>1012</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>127</v>
@@ -20297,7 +20300,7 @@
         <v>46064</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>573</v>
+        <v>1012</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>144</v>
@@ -20383,7 +20386,7 @@
         <v>46065</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>573</v>
+        <v>1012</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>29</v>
@@ -20469,7 +20472,7 @@
         <v>46066</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>573</v>
+        <v>1012</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>51</v>
@@ -20555,7 +20558,7 @@
         <v>46067</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>573</v>
+        <v>1012</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>70</v>
@@ -20641,7 +20644,7 @@
         <v>46068</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>573</v>
+        <v>1012</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>90</v>
@@ -20727,7 +20730,7 @@
         <v>46069</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>573</v>
+        <v>1012</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>110</v>
@@ -20813,7 +20816,7 @@
         <v>46070</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>573</v>
+        <v>1012</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>127</v>
@@ -20899,7 +20902,7 @@
         <v>46071</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>573</v>
+        <v>1012</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>144</v>
@@ -20985,7 +20988,7 @@
         <v>46072</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>573</v>
+        <v>1012</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>29</v>
@@ -21071,7 +21074,7 @@
         <v>46073</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>573</v>
+        <v>1012</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>51</v>
@@ -21157,7 +21160,7 @@
         <v>46074</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>573</v>
+        <v>1012</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>70</v>
@@ -21243,7 +21246,7 @@
         <v>46075</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>573</v>
+        <v>1012</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>90</v>
@@ -21329,7 +21332,7 @@
         <v>46076</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>573</v>
+        <v>1012</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>110</v>
@@ -21415,7 +21418,7 @@
         <v>46077</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>573</v>
+        <v>1012</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>127</v>
@@ -21501,7 +21504,7 @@
         <v>46078</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>573</v>
+        <v>1012</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>144</v>
@@ -21587,7 +21590,7 @@
         <v>46079</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>573</v>
+        <v>1012</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>29</v>
@@ -21673,7 +21676,7 @@
         <v>46080</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>573</v>
+        <v>1012</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>51</v>
@@ -21759,7 +21762,7 @@
         <v>46081</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>573</v>
+        <v>1012</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>70</v>
@@ -21845,7 +21848,7 @@
         <v>46082</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>573</v>
+        <v>1012</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>90</v>
@@ -21931,7 +21934,7 @@
         <v>46083</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>573</v>
+        <v>1012</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>110</v>
@@ -22017,7 +22020,7 @@
         <v>46084</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>573</v>
+        <v>1012</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>127</v>
@@ -22103,7 +22106,7 @@
         <v>46085</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>1012</v>
+        <v>1437</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>144</v>
@@ -22189,7 +22192,7 @@
         <v>46086</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>1012</v>
+        <v>1437</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>29</v>
@@ -22275,7 +22278,7 @@
         <v>46087</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>1012</v>
+        <v>1437</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>51</v>
@@ -22361,7 +22364,7 @@
         <v>46088</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>1012</v>
+        <v>1437</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>70</v>
@@ -22447,7 +22450,7 @@
         <v>46089</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>1012</v>
+        <v>1437</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>90</v>
@@ -22533,7 +22536,7 @@
         <v>46090</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>1012</v>
+        <v>1437</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>110</v>
@@ -22619,7 +22622,7 @@
         <v>46091</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>1012</v>
+        <v>1437</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>127</v>
@@ -22705,7 +22708,7 @@
         <v>46092</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>1012</v>
+        <v>1437</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>144</v>
@@ -22791,7 +22794,7 @@
         <v>46093</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>1012</v>
+        <v>1437</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>29</v>
@@ -22877,7 +22880,7 @@
         <v>46094</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>1012</v>
+        <v>1437</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>51</v>
@@ -22963,7 +22966,7 @@
         <v>46095</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>1012</v>
+        <v>1437</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>70</v>
@@ -23049,7 +23052,7 @@
         <v>46096</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>1012</v>
+        <v>1437</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>90</v>
@@ -23135,7 +23138,7 @@
         <v>46097</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>1012</v>
+        <v>1437</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>110</v>
@@ -23221,7 +23224,7 @@
         <v>46098</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>1012</v>
+        <v>1437</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>127</v>
@@ -23307,7 +23310,7 @@
         <v>46099</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>1012</v>
+        <v>1437</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>144</v>
@@ -23393,7 +23396,7 @@
         <v>46100</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>1012</v>
+        <v>1437</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>29</v>
@@ -23479,7 +23482,7 @@
         <v>46101</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>1012</v>
+        <v>1437</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>51</v>
@@ -23565,7 +23568,7 @@
         <v>46102</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>1012</v>
+        <v>1437</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>70</v>
@@ -23651,7 +23654,7 @@
         <v>46103</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>1012</v>
+        <v>1437</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>90</v>
@@ -23737,7 +23740,7 @@
         <v>46104</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>1012</v>
+        <v>1437</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>110</v>
@@ -23823,7 +23826,7 @@
         <v>46105</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>1012</v>
+        <v>1437</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>127</v>
@@ -23909,7 +23912,7 @@
         <v>46106</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>1012</v>
+        <v>1437</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>144</v>
@@ -23995,7 +23998,7 @@
         <v>46107</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>1012</v>
+        <v>1437</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>29</v>
@@ -24081,7 +24084,7 @@
         <v>46108</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>1012</v>
+        <v>1437</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>51</v>
@@ -24167,7 +24170,7 @@
         <v>46109</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>1012</v>
+        <v>1437</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>70</v>
@@ -24253,7 +24256,7 @@
         <v>46110</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>1012</v>
+        <v>1437</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>90</v>
@@ -24339,7 +24342,7 @@
         <v>46111</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>1012</v>
+        <v>1437</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>110</v>
@@ -24425,7 +24428,7 @@
         <v>46112</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>1012</v>
+        <v>1437</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>127</v>
@@ -24511,7 +24514,7 @@
         <v>46113</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>1012</v>
+        <v>1437</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>144</v>
@@ -24597,7 +24600,7 @@
         <v>46114</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>1437</v>
+        <v>1876</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>29</v>
@@ -24683,7 +24686,7 @@
         <v>46115</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>1437</v>
+        <v>1876</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>51</v>
@@ -24769,7 +24772,7 @@
         <v>46116</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>1437</v>
+        <v>1876</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>70</v>
@@ -24855,7 +24858,7 @@
         <v>46117</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>1437</v>
+        <v>1876</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>90</v>
@@ -24941,7 +24944,7 @@
         <v>46118</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>1437</v>
+        <v>1876</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>110</v>
@@ -25027,7 +25030,7 @@
         <v>46119</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>1437</v>
+        <v>1876</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>127</v>
@@ -25113,7 +25116,7 @@
         <v>46120</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>1437</v>
+        <v>1876</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>144</v>
@@ -25199,7 +25202,7 @@
         <v>46121</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>1437</v>
+        <v>1876</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>29</v>
@@ -25285,7 +25288,7 @@
         <v>46122</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>1437</v>
+        <v>1876</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>51</v>
@@ -25371,7 +25374,7 @@
         <v>46123</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>1437</v>
+        <v>1876</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>70</v>
@@ -25457,7 +25460,7 @@
         <v>46124</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>1437</v>
+        <v>1876</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>90</v>
@@ -25543,7 +25546,7 @@
         <v>46125</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>1437</v>
+        <v>1876</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>110</v>
@@ -25629,7 +25632,7 @@
         <v>46126</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>1437</v>
+        <v>1876</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>127</v>
@@ -25715,7 +25718,7 @@
         <v>46127</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>1437</v>
+        <v>1876</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>144</v>
@@ -25801,7 +25804,7 @@
         <v>46128</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>1437</v>
+        <v>1876</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>29</v>
@@ -25887,7 +25890,7 @@
         <v>46129</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>1437</v>
+        <v>1876</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>51</v>
@@ -25973,7 +25976,7 @@
         <v>46130</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>1437</v>
+        <v>1876</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>70</v>
@@ -26059,7 +26062,7 @@
         <v>46131</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>1437</v>
+        <v>1876</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>90</v>
@@ -26145,7 +26148,7 @@
         <v>46132</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>1437</v>
+        <v>1876</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>110</v>
@@ -26231,7 +26234,7 @@
         <v>46133</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>1437</v>
+        <v>1876</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>127</v>
@@ -26317,7 +26320,7 @@
         <v>46134</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>1437</v>
+        <v>1876</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>144</v>
@@ -26403,7 +26406,7 @@
         <v>46135</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>1437</v>
+        <v>1876</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>29</v>
@@ -26489,7 +26492,7 @@
         <v>46136</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>1437</v>
+        <v>1876</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>51</v>
@@ -26575,7 +26578,7 @@
         <v>46137</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>1437</v>
+        <v>1876</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>70</v>
@@ -26661,7 +26664,7 @@
         <v>46138</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>1437</v>
+        <v>1876</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>90</v>
@@ -26747,7 +26750,7 @@
         <v>46139</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>1437</v>
+        <v>1876</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>110</v>
@@ -26833,7 +26836,7 @@
         <v>46140</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>1437</v>
+        <v>1876</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>127</v>
@@ -26919,7 +26922,7 @@
         <v>46141</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>1437</v>
+        <v>1876</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>144</v>
@@ -27005,7 +27008,7 @@
         <v>46142</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>1437</v>
+        <v>1876</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>29</v>
@@ -27091,7 +27094,7 @@
         <v>46143</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>1437</v>
+        <v>1876</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>51</v>
@@ -27177,7 +27180,7 @@
         <v>46144</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>1876</v>
+        <v>2315</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>70</v>
@@ -27263,7 +27266,7 @@
         <v>46145</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>1876</v>
+        <v>2315</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>90</v>
@@ -27349,7 +27352,7 @@
         <v>46146</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>1876</v>
+        <v>2315</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>110</v>
@@ -27435,7 +27438,7 @@
         <v>46147</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>1876</v>
+        <v>2315</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>127</v>
@@ -27521,7 +27524,7 @@
         <v>46148</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>1876</v>
+        <v>2315</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>144</v>
@@ -27607,7 +27610,7 @@
         <v>46149</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>1876</v>
+        <v>2315</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>29</v>
@@ -27693,7 +27696,7 @@
         <v>46150</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>1876</v>
+        <v>2315</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>51</v>
@@ -27779,7 +27782,7 @@
         <v>46151</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>1876</v>
+        <v>2315</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>70</v>
@@ -27865,7 +27868,7 @@
         <v>46152</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>1876</v>
+        <v>2315</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>90</v>
@@ -27951,7 +27954,7 @@
         <v>46153</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>1876</v>
+        <v>2315</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>110</v>
@@ -28037,7 +28040,7 @@
         <v>46154</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>1876</v>
+        <v>2315</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>127</v>
@@ -28123,7 +28126,7 @@
         <v>46155</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>1876</v>
+        <v>2315</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>144</v>
@@ -28209,7 +28212,7 @@
         <v>46156</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>1876</v>
+        <v>2315</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>29</v>
@@ -28295,7 +28298,7 @@
         <v>46157</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>1876</v>
+        <v>2315</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>51</v>
@@ -28381,7 +28384,7 @@
         <v>46158</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>1876</v>
+        <v>2315</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>70</v>
@@ -28467,7 +28470,7 @@
         <v>46159</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>1876</v>
+        <v>5418</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>90</v>
@@ -28553,7 +28556,7 @@
         <v>46160</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>1876</v>
+        <v>5418</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>110</v>
@@ -28639,7 +28642,7 @@
         <v>46161</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>1876</v>
+        <v>5418</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>127</v>
@@ -28725,7 +28728,7 @@
         <v>46162</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>1876</v>
+        <v>5418</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>144</v>
@@ -28811,7 +28814,7 @@
         <v>46163</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>1876</v>
+        <v>5418</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>29</v>
@@ -28897,7 +28900,7 @@
         <v>46164</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>1876</v>
+        <v>5418</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>51</v>
@@ -28983,7 +28986,7 @@
         <v>46165</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>1876</v>
+        <v>5418</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>70</v>
@@ -29069,7 +29072,7 @@
         <v>46166</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>1876</v>
+        <v>5418</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>90</v>
@@ -29155,7 +29158,7 @@
         <v>46167</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>1876</v>
+        <v>5418</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>110</v>
@@ -29241,7 +29244,7 @@
         <v>46168</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>1876</v>
+        <v>5418</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>127</v>
@@ -29327,7 +29330,7 @@
         <v>46169</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>1876</v>
+        <v>5418</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>144</v>
@@ -29413,7 +29416,7 @@
         <v>46170</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>1876</v>
+        <v>5418</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>29</v>
@@ -29499,7 +29502,7 @@
         <v>46171</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>1876</v>
+        <v>5418</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>51</v>
@@ -29585,7 +29588,7 @@
         <v>46172</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>1876</v>
+        <v>5418</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>70</v>
@@ -29671,7 +29674,7 @@
         <v>46173</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>1876</v>
+        <v>5418</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>90</v>
@@ -29757,7 +29760,7 @@
         <v>46174</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>2315</v>
+        <v>5418</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>110</v>
@@ -29843,7 +29846,7 @@
         <v>46175</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>2315</v>
+        <v>5418</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>127</v>
@@ -29929,7 +29932,7 @@
         <v>46176</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>2315</v>
+        <v>5418</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>144</v>
@@ -30015,7 +30018,7 @@
         <v>46177</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>2315</v>
+        <v>5418</v>
       </c>
       <c r="C156" s="2" t="s">
         <v>29</v>
@@ -30101,7 +30104,7 @@
         <v>46178</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>2315</v>
+        <v>5418</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>51</v>
@@ -30187,7 +30190,7 @@
         <v>46179</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>2315</v>
+        <v>5418</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>70</v>
@@ -30273,7 +30276,7 @@
         <v>46180</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>2315</v>
+        <v>5418</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>90</v>
@@ -30359,7 +30362,7 @@
         <v>46181</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>2315</v>
+        <v>5418</v>
       </c>
       <c r="C160" s="2" t="s">
         <v>110</v>
@@ -30445,7 +30448,7 @@
         <v>46182</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>2315</v>
+        <v>5418</v>
       </c>
       <c r="C161" s="2" t="s">
         <v>127</v>
@@ -30531,7 +30534,7 @@
         <v>46183</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>2315</v>
+        <v>5418</v>
       </c>
       <c r="C162" s="2" t="s">
         <v>144</v>
@@ -30617,7 +30620,7 @@
         <v>46184</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>2315</v>
+        <v>5418</v>
       </c>
       <c r="C163" s="2" t="s">
         <v>29</v>
@@ -30703,7 +30706,7 @@
         <v>46185</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>2315</v>
+        <v>5418</v>
       </c>
       <c r="C164" s="2" t="s">
         <v>51</v>
@@ -30789,7 +30792,7 @@
         <v>46186</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>2315</v>
+        <v>5418</v>
       </c>
       <c r="C165" s="2" t="s">
         <v>70</v>
@@ -30875,7 +30878,7 @@
         <v>46187</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>2315</v>
+        <v>5418</v>
       </c>
       <c r="C166" s="2" t="s">
         <v>90</v>
